--- a/data/trans_dic/P1412-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1412-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,3</t>
+          <t>0,75; 2,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,84</t>
+          <t>1,04; 2,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,6</t>
+          <t>1,13; 3,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,45</t>
+          <t>1,03; 2,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,33</t>
+          <t>0,69; 2,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,97</t>
+          <t>0,89; 2,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,05</t>
+          <t>1,1; 2,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,23</t>
+          <t>1,03; 2,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,32</t>
+          <t>1,16; 2,35</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,95</t>
+          <t>0,21; 0,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,79</t>
+          <t>0,21; 0,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,93</t>
+          <t>0,38; 1,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,61</t>
+          <t>0,06; 0,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,55</t>
+          <t>0,21; 0,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,59</t>
+          <t>0,16; 0,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,55</t>
+          <t>0,18; 0,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,64</t>
+          <t>0,36; 0,76</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -903,42 +903,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,3</t>
+          <t>0,17; 1,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,78</t>
+          <t>0,43; 1,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,08</t>
+          <t>0,09; 1,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,01</t>
+          <t>0,29; 0,93</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,01</t>
+          <t>0,43; 1,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,1</t>
+          <t>0,52; 1,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,21</t>
+          <t>0,66; 1,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,02</t>
+          <t>0,46; 1,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,83</t>
+          <t>0,34; 0,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,7</t>
+          <t>0,41; 0,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,92</t>
+          <t>0,5; 0,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,87</t>
+          <t>0,47; 0,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,85</t>
+          <t>0,59; 0,93</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20907</t>
+          <t>23189</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7343; 22429</t>
+          <t>7323; 22036</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7960; 21410</t>
+          <t>7850; 21817</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6642; 18438</t>
+          <t>6525; 20533</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13974; 32685</t>
+          <t>13718; 32503</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7020; 23139</t>
+          <t>6870; 22303</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5861; 14804</t>
+          <t>7286; 16654</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24205; 47463</t>
+          <t>25356; 49545</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18608; 39086</t>
+          <t>18047; 38148</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14800; 29386</t>
+          <t>16173; 32853</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>14025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19812</t>
+          <t>22667</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4119; 18593</t>
+          <t>4204; 19347</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3443; 16466</t>
+          <t>4270; 16601</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7393; 21202</t>
+          <t>8388; 22760</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7500</t>
+          <t>0; 6674</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1172; 12095</t>
+          <t>1261; 11953</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3526; 12353</t>
+          <t>4591; 13905</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5251; 22081</t>
+          <t>6113; 20864</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6802; 22369</t>
+          <t>7325; 23282</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12857; 29147</t>
+          <t>15620; 33372</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>7786</t>
         </is>
       </c>
     </row>
@@ -1637,42 +1637,42 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>937; 12565</t>
+          <t>916; 10791</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2819; 11484</t>
+          <t>3083; 11759</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5933</t>
+          <t>0; 5379</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4178</t>
+          <t>0; 4475</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4377</t>
+          <t>0; 4365</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6174</t>
+          <t>0; 5256</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1146; 11853</t>
+          <t>1030; 13113</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3868; 13163</t>
+          <t>4163; 13459</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>32671</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>20972</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>53643</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14692; 34488</t>
+          <t>14566; 36384</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17414; 37270</t>
+          <t>17481; 38330</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21390; 41599</t>
+          <t>23130; 44479</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15622; 36302</t>
+          <t>16392; 37011</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10262; 29389</t>
+          <t>12089; 30379</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12487; 25679</t>
+          <t>15112; 29724</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34756; 64115</t>
+          <t>34957; 63573</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33273; 59886</t>
+          <t>32699; 61909</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35961; 60559</t>
+          <t>43044; 67513</t>
         </is>
       </c>
     </row>
